--- a/Result/profitability/6721.xlsx
+++ b/Result/profitability/6721.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM31"/>
+  <dimension ref="A1:AM32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4367,6 +4367,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6721</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>912</v>
+      </c>
+      <c r="D32" t="n">
+        <v>857</v>
+      </c>
+      <c r="E32" t="n">
+        <v>55</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>39</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>4.26%</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>41</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.23375</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.3175</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W32" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="X32" t="n">
+        <v>-0.05405405405405406</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-0.01948051948051954</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.2799999999999998</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.2499999999999998</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.1615384615384614</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK32" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
